--- a/data/trans_dic/P19C04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 14,21</t>
+          <t>7,99; 14,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,71</t>
+          <t>10,31; 17,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,72</t>
+          <t>6,31; 12,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 13,77</t>
+          <t>3,55; 13,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,74</t>
+          <t>5,29; 10,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,95; 16,86</t>
+          <t>9,71; 16,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 11,67</t>
+          <t>5,93; 11,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,39</t>
+          <t>1,8; 6,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 11,71</t>
+          <t>7,33; 11,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,02</t>
+          <t>11,04; 16,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,01</t>
+          <t>6,88; 11,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,64</t>
+          <t>3,65; 9,76</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 17,66</t>
+          <t>11,23; 17,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 21,96</t>
+          <t>15,47; 22,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 17,75</t>
+          <t>11,34; 18,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 15,26</t>
+          <t>7,57; 15,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 13,99</t>
+          <t>8,29; 13,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 14,79</t>
+          <t>9,38; 14,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,98</t>
+          <t>9,3; 15,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,67</t>
+          <t>4,19; 10,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,46; 14,55</t>
+          <t>10,68; 14,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,01; 17,29</t>
+          <t>13,17; 17,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,15; 15,31</t>
+          <t>11,22; 15,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,74</t>
+          <t>6,48; 11,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,53; 22,72</t>
+          <t>15,2; 22,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,45; 26,67</t>
+          <t>19,61; 26,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 17,22</t>
+          <t>11,31; 17,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 14,71</t>
+          <t>9,05; 14,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 15,99</t>
+          <t>10,29; 15,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,94; 17,56</t>
+          <t>11,84; 17,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 13,18</t>
+          <t>8,21; 13,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,76</t>
+          <t>6,69; 10,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,26; 17,84</t>
+          <t>13,34; 17,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,13; 20,7</t>
+          <t>16,12; 20,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,36; 14,47</t>
+          <t>10,35; 14,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 11,89</t>
+          <t>8,48; 11,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,2; 32,43</t>
+          <t>22,79; 31,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,73; 28,88</t>
+          <t>21,04; 29,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 21,71</t>
+          <t>14,76; 21,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 15,19</t>
+          <t>4,55; 15,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 24,0</t>
+          <t>16,4; 23,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,57; 21,6</t>
+          <t>14,68; 22,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,19</t>
+          <t>9,27; 14,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,01</t>
+          <t>7,33; 10,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,7; 26,7</t>
+          <t>20,57; 26,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,79; 24,09</t>
+          <t>18,89; 23,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,42; 17,2</t>
+          <t>12,64; 17,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,34</t>
+          <t>5,62; 12,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,45; 32,17</t>
+          <t>20,95; 31,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,14; 37,12</t>
+          <t>26,66; 36,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,0; 31,44</t>
+          <t>21,61; 30,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 23,22</t>
+          <t>16,64; 22,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 24,93</t>
+          <t>16,15; 25,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 26,85</t>
+          <t>18,0; 26,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 17,29</t>
+          <t>9,74; 16,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 16,18</t>
+          <t>11,71; 16,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,49; 26,4</t>
+          <t>19,65; 26,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,82; 30,56</t>
+          <t>23,47; 30,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 22,84</t>
+          <t>16,54; 23,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,91; 18,91</t>
+          <t>15,19; 18,9</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,89; 36,24</t>
+          <t>23,39; 35,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,85; 45,75</t>
+          <t>32,73; 45,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,4; 32,83</t>
+          <t>21,31; 33,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,59; 26,86</t>
+          <t>19,91; 26,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,52; 24,77</t>
+          <t>15,36; 24,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,18; 28,94</t>
+          <t>19,11; 29,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,18; 22,29</t>
+          <t>13,24; 22,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 16,51</t>
+          <t>4,01; 16,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,07; 27,76</t>
+          <t>20,43; 28,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,67; 34,67</t>
+          <t>26,79; 35,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,42; 25,66</t>
+          <t>18,13; 25,77</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,09; 20,35</t>
+          <t>7,81; 20,22</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,41; 33,17</t>
+          <t>17,67; 32,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,84; 48,03</t>
+          <t>31,7; 48,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,95; 34,92</t>
+          <t>21,78; 35,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,04; 29,13</t>
+          <t>21,69; 29,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,1; 22,63</t>
+          <t>11,55; 22,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,2; 32,48</t>
+          <t>21,92; 32,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,47; 32,75</t>
+          <t>19,4; 32,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,77; 22,09</t>
+          <t>16,68; 22,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,54; 24,87</t>
+          <t>15,37; 24,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,42; 36,75</t>
+          <t>27,33; 36,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,88; 31,07</t>
+          <t>21,67; 31,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,74; 24,12</t>
+          <t>19,78; 24,41</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,37; 21,65</t>
+          <t>18,3; 21,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,07; 26,49</t>
+          <t>23,2; 26,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,39; 19,45</t>
+          <t>16,41; 19,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,24</t>
+          <t>11,22; 16,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,96</t>
+          <t>13,46; 16,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,21; 18,88</t>
+          <t>16,13; 18,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,7; 14,42</t>
+          <t>11,64; 14,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,67</t>
+          <t>8,53; 11,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,06; 18,26</t>
+          <t>16,14; 18,21</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,98; 22,12</t>
+          <t>19,87; 22,09</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,36; 16,34</t>
+          <t>14,4; 16,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,75; 13,57</t>
+          <t>10,93; 13,63</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28862; 51062</t>
+          <t>28719; 51685</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40249; 67154</t>
+          <t>39087; 66703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22405; 44866</t>
+          <t>22267; 44944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14431; 52784</t>
+          <t>13606; 51643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20614; 40428</t>
+          <t>19904; 39946</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36901; 62545</t>
+          <t>36013; 61587</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21360; 41068</t>
+          <t>20874; 41742</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5641; 22417</t>
+          <t>5465; 20953</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52899; 86138</t>
+          <t>53958; 84073</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82265; 120142</t>
+          <t>82852; 122629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48351; 77573</t>
+          <t>48459; 79287</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23797; 66205</t>
+          <t>25075; 67080</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64284; 101705</t>
+          <t>64673; 98302</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92010; 131165</t>
+          <t>92412; 132298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56630; 87510</t>
+          <t>55928; 89229</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30201; 61410</t>
+          <t>30456; 63772</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46111; 76621</t>
+          <t>45427; 75811</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52527; 82476</t>
+          <t>52324; 83578</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46005; 74431</t>
+          <t>46191; 75405</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22452; 53323</t>
+          <t>20951; 51781</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117518; 163470</t>
+          <t>120018; 163870</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>150233; 199724</t>
+          <t>152158; 201459</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110400; 151557</t>
+          <t>111026; 152855</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60118; 105872</t>
+          <t>58489; 105158</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78091; 114259</t>
+          <t>76446; 110979</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>114133; 156451</t>
+          <t>115032; 155466</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63646; 96083</t>
+          <t>63106; 95878</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45830; 76923</t>
+          <t>47325; 78175</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62085; 96512</t>
+          <t>62113; 94221</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78755; 115824</t>
+          <t>78097; 116482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45796; 75516</t>
+          <t>47038; 75160</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36246; 57235</t>
+          <t>35582; 57916</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>146670; 197390</t>
+          <t>147600; 196525</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200991; 257921</t>
+          <t>200876; 255822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117121; 163671</t>
+          <t>116999; 162790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89791; 125461</t>
+          <t>89466; 125059</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93898; 131268</t>
+          <t>92232; 129490</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>112517; 156790</t>
+          <t>114226; 159338</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75203; 111253</t>
+          <t>75603; 112460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37499; 131110</t>
+          <t>39234; 131508</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72559; 105409</t>
+          <t>72040; 104362</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82094; 121696</t>
+          <t>82689; 124909</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51087; 82783</t>
+          <t>50527; 81457</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51834; 77166</t>
+          <t>51382; 76559</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>174731; 225347</t>
+          <t>173584; 224742</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>207853; 266434</t>
+          <t>209005; 264663</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131310; 181833</t>
+          <t>133668; 183172</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89972; 192938</t>
+          <t>87861; 192189</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>58414; 87618</t>
+          <t>57044; 85078</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>98047; 134135</t>
+          <t>96320; 133566</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>81627; 116646</t>
+          <t>80166; 114554</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93572; 126913</t>
+          <t>90937; 124655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50763; 79545</t>
+          <t>51523; 80273</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70248; 104644</t>
+          <t>70138; 104765</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39276; 68239</t>
+          <t>38438; 66259</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>63465; 86497</t>
+          <t>62610; 85849</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>115276; 156165</t>
+          <t>116196; 157698</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>178864; 229496</t>
+          <t>176231; 226087</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>128142; 174923</t>
+          <t>126651; 176143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>161179; 204450</t>
+          <t>164207; 204371</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>50836; 77115</t>
+          <t>49767; 76237</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86224; 120081</t>
+          <t>85923; 119197</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49253; 75545</t>
+          <t>49032; 76322</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70386; 96510</t>
+          <t>71535; 96937</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38331; 61166</t>
+          <t>37922; 61711</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57639; 87002</t>
+          <t>57451; 87786</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36494; 61725</t>
+          <t>36674; 62357</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22524; 99062</t>
+          <t>24033; 100474</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92247; 127603</t>
+          <t>93900; 129805</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>150185; 195227</t>
+          <t>150844; 197296</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93410; 130128</t>
+          <t>91936; 130684</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>77649; 195240</t>
+          <t>74959; 193941</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22072; 42042</t>
+          <t>22398; 41314</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58888; 88820</t>
+          <t>58616; 89406</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32277; 51354</t>
+          <t>32027; 52441</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57956; 80251</t>
+          <t>59772; 80584</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23121; 47109</t>
+          <t>24049; 46369</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67368; 98546</t>
+          <t>66518; 98517</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44367; 74623</t>
+          <t>44216; 74246</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>68528; 90288</t>
+          <t>68164; 90714</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52038; 83293</t>
+          <t>51496; 82722</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>133888; 179479</t>
+          <t>133474; 177661</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82024; 116494</t>
+          <t>81240; 116971</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>135061; 165009</t>
+          <t>135330; 167002</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>450878; 531386</t>
+          <t>449175; 530224</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>672392; 772075</t>
+          <t>676315; 774731</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>436630; 518235</t>
+          <t>437264; 516550</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>374856; 544619</t>
+          <t>376258; 540180</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>364094; 437561</t>
+          <t>368865; 439813</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>509695; 593783</t>
+          <t>507321; 592332</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>335473; 413296</t>
+          <t>333507; 410704</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>308764; 417583</t>
+          <t>305337; 415367</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>834415; 948895</t>
+          <t>838333; 946159</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1210693; 1340636</t>
+          <t>1204086; 1338789</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>794359; 903583</t>
+          <t>796671; 906223</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>745530; 940970</t>
+          <t>757706; 944760</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 14,38</t>
+          <t>7,75; 14,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,31; 17,59</t>
+          <t>10,37; 17,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,74</t>
+          <t>6,5; 12,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 13,47</t>
+          <t>4,17; 14,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 10,62</t>
+          <t>5,32; 10,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 16,6</t>
+          <t>9,87; 16,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,86</t>
+          <t>5,81; 11,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,9</t>
+          <t>2,17; 7,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,43</t>
+          <t>7,17; 11,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 16,35</t>
+          <t>11,28; 16,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 11,25</t>
+          <t>6,75; 11,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,76</t>
+          <t>3,9; 9,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,23; 17,07</t>
+          <t>11,25; 17,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 22,15</t>
+          <t>15,71; 21,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 18,1</t>
+          <t>11,27; 17,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,85</t>
+          <t>8,15; 15,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,84</t>
+          <t>8,45; 13,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 14,99</t>
+          <t>9,42; 14,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 15,18</t>
+          <t>9,42; 14,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,36</t>
+          <t>6,7; 12,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,68; 14,59</t>
+          <t>10,48; 14,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,17; 17,44</t>
+          <t>13,16; 17,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 15,44</t>
+          <t>11,15; 15,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 11,66</t>
+          <t>8,3; 13,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,2; 22,07</t>
+          <t>15,06; 22,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,61; 26,5</t>
+          <t>19,58; 26,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 17,19</t>
+          <t>11,38; 17,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,95</t>
+          <t>10,99; 17,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 15,61</t>
+          <t>10,17; 15,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 17,66</t>
+          <t>11,76; 17,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 13,12</t>
+          <t>8,28; 13,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,89</t>
+          <t>7,23; 11,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,34; 17,76</t>
+          <t>13,2; 17,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,12; 20,53</t>
+          <t>16,31; 20,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 14,39</t>
+          <t>10,55; 14,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,86</t>
+          <t>9,54; 13,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,79; 31,99</t>
+          <t>22,58; 32,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,04; 29,35</t>
+          <t>20,76; 28,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 21,95</t>
+          <t>14,75; 21,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 15,24</t>
+          <t>12,51; 17,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,4; 23,76</t>
+          <t>16,37; 24,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 22,17</t>
+          <t>14,99; 22,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 14,95</t>
+          <t>9,19; 14,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 10,93</t>
+          <t>7,97; 11,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,57; 26,63</t>
+          <t>20,67; 26,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 23,93</t>
+          <t>18,91; 23,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 17,33</t>
+          <t>12,69; 17,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 12,29</t>
+          <t>10,8; 14,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,95; 31,24</t>
+          <t>21,13; 31,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,66; 36,97</t>
+          <t>27,17; 37,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,61; 30,88</t>
+          <t>22,24; 31,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,64; 22,81</t>
+          <t>17,64; 23,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,15; 25,16</t>
+          <t>15,87; 24,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,0; 26,88</t>
+          <t>18,3; 27,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,74; 16,78</t>
+          <t>9,93; 17,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,71; 16,06</t>
+          <t>11,76; 16,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,65; 26,66</t>
+          <t>19,71; 26,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,47; 30,1</t>
+          <t>23,87; 30,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,54; 23,0</t>
+          <t>16,75; 22,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,19; 18,9</t>
+          <t>15,37; 19,04</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,39; 35,83</t>
+          <t>23,88; 35,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,73; 45,41</t>
+          <t>32,68; 45,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21,31; 33,17</t>
+          <t>21,49; 32,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,91; 26,98</t>
+          <t>19,51; 26,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,36; 24,99</t>
+          <t>15,52; 24,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,11; 29,2</t>
+          <t>19,17; 28,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,24; 22,52</t>
+          <t>13,48; 22,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 16,75</t>
+          <t>13,29; 18,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,43; 28,24</t>
+          <t>21,13; 28,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,79; 35,04</t>
+          <t>26,37; 34,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,13; 25,77</t>
+          <t>18,16; 25,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,81; 20,22</t>
+          <t>17,09; 21,37</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,67; 32,59</t>
+          <t>17,03; 32,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,7; 48,35</t>
+          <t>32,8; 47,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,78; 35,66</t>
+          <t>21,61; 35,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,69; 29,25</t>
+          <t>20,95; 29,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,55; 22,27</t>
+          <t>11,64; 22,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,92; 32,47</t>
+          <t>21,94; 31,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,4; 32,58</t>
+          <t>18,96; 32,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,68; 22,2</t>
+          <t>16,5; 21,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,37; 24,7</t>
+          <t>15,38; 24,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,33; 36,38</t>
+          <t>27,82; 36,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,67; 31,2</t>
+          <t>21,14; 31,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,78; 24,41</t>
+          <t>19,02; 23,47</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,3; 21,6</t>
+          <t>18,43; 21,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,2; 26,58</t>
+          <t>22,96; 26,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,41; 19,39</t>
+          <t>16,5; 19,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,11</t>
+          <t>14,83; 17,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,46; 16,05</t>
+          <t>13,43; 16,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,13; 18,83</t>
+          <t>16,28; 19,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,64; 14,33</t>
+          <t>11,77; 14,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,61</t>
+          <t>10,7; 12,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,21</t>
+          <t>16,14; 18,29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,87; 22,09</t>
+          <t>19,9; 22,08</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,4; 16,39</t>
+          <t>14,29; 16,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,93; 13,63</t>
+          <t>13,05; 14,63</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40349</t>
+          <t>45029</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28719; 51685</t>
+          <t>27859; 51373</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39087; 66703</t>
+          <t>39310; 67262</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22267; 44944</t>
+          <t>22928; 45473</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13606; 51643</t>
+          <t>15806; 53728</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19904; 39946</t>
+          <t>20024; 40339</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36013; 61587</t>
+          <t>36635; 62175</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20874; 41742</t>
+          <t>20457; 42118</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5465; 20953</t>
+          <t>7442; 26780</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53958; 84073</t>
+          <t>52773; 83756</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82852; 122629</t>
+          <t>84586; 122681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48459; 79287</t>
+          <t>47593; 79017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25075; 67080</t>
+          <t>28172; 66965</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44742</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37274</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82016</t>
+          <t>96360</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64673; 98302</t>
+          <t>64801; 99245</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92412; 132298</t>
+          <t>93802; 131131</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55928; 89229</t>
+          <t>55556; 87168</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30456; 63772</t>
+          <t>36358; 71245</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45427; 75811</t>
+          <t>46274; 75497</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52324; 83578</t>
+          <t>52554; 82763</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46191; 75405</t>
+          <t>46783; 73925</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20951; 51781</t>
+          <t>32356; 57936</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120018; 163870</t>
+          <t>117729; 162685</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152158; 201459</t>
+          <t>151949; 201899</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111026; 152855</t>
+          <t>110397; 152858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58489; 105158</t>
+          <t>77093; 121758</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>82242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>54728</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>106735</t>
+          <t>136970</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76446; 110979</t>
+          <t>75738; 110891</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>115032; 155466</t>
+          <t>114838; 155167</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63106; 95878</t>
+          <t>63496; 97411</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47325; 78175</t>
+          <t>65923; 102584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62113; 94221</t>
+          <t>61398; 94064</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78097; 116482</t>
+          <t>77564; 113145</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47038; 75160</t>
+          <t>47430; 75892</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35582; 57916</t>
+          <t>43936; 67151</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>147600; 196525</t>
+          <t>146027; 194879</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200876; 255822</t>
+          <t>203301; 258538</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116999; 162790</t>
+          <t>119327; 162768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89466; 125059</t>
+          <t>115214; 159099</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>103276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>64312</t>
+          <t>69518</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>153408</t>
+          <t>172794</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92232; 129490</t>
+          <t>91410; 130076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>114226; 159338</t>
+          <t>112694; 155237</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>75603; 112460</t>
+          <t>75590; 112180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39234; 131508</t>
+          <t>84844; 121010</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72040; 104362</t>
+          <t>71912; 105580</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82689; 124909</t>
+          <t>84454; 124130</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50527; 81457</t>
+          <t>50102; 81234</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51382; 76559</t>
+          <t>57554; 82537</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>173584; 224742</t>
+          <t>174467; 225083</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>209005; 264663</t>
+          <t>209137; 264824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>133668; 183172</t>
+          <t>134188; 181660</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>87861; 192189</t>
+          <t>151213; 199083</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108312</t>
+          <t>122048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74245</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>182557</t>
+          <t>204362</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57044; 85078</t>
+          <t>57553; 86978</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96320; 133566</t>
+          <t>98172; 136187</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80166; 114554</t>
+          <t>82493; 117834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90937; 124655</t>
+          <t>104668; 140417</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51523; 80273</t>
+          <t>50635; 78866</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70138; 104765</t>
+          <t>71330; 105541</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38438; 66259</t>
+          <t>39195; 68034</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>62610; 85849</t>
+          <t>70092; 95478</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>116196; 157698</t>
+          <t>116573; 157347</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>176231; 226087</t>
+          <t>179279; 227392</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>126651; 176143</t>
+          <t>128282; 174311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>164207; 204371</t>
+          <t>182781; 226370</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83938</t>
+          <t>90799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>63249</t>
+          <t>67703</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>147187</t>
+          <t>158502</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>49767; 76237</t>
+          <t>50798; 76512</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>85923; 119197</t>
+          <t>85783; 120343</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49032; 76322</t>
+          <t>49462; 75869</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71535; 96937</t>
+          <t>77600; 106767</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37922; 61711</t>
+          <t>38323; 61060</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>57451; 87786</t>
+          <t>57618; 86350</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36674; 62357</t>
+          <t>37340; 63634</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24033; 100474</t>
+          <t>57016; 78740</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>93900; 129805</t>
+          <t>97114; 131527</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>150844; 197296</t>
+          <t>148507; 196420</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91936; 130684</t>
+          <t>92075; 129908</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>74959; 193941</t>
+          <t>141313; 176672</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69878</t>
+          <t>74747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>79249</t>
+          <t>84268</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>149127</t>
+          <t>159015</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22398; 41314</t>
+          <t>21583; 41292</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>58616; 89406</t>
+          <t>60664; 87923</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32027; 52441</t>
+          <t>31773; 51676</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59772; 80584</t>
+          <t>63343; 87836</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24049; 46369</t>
+          <t>24229; 47109</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>66518; 98517</t>
+          <t>66574; 97048</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44216; 74246</t>
+          <t>43217; 74341</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>68164; 90714</t>
+          <t>73559; 96680</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>51496; 82722</t>
+          <t>51503; 81648</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>133474; 177661</t>
+          <t>135852; 176175</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81240; 116971</t>
+          <t>79277; 118589</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>135330; 167002</t>
+          <t>142281; 175619</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>484977</t>
+          <t>555917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>376402</t>
+          <t>417116</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>861379</t>
+          <t>973032</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>449175; 530224</t>
+          <t>452315; 532460</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>676315; 774731</t>
+          <t>669120; 766749</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>437264; 516550</t>
+          <t>439636; 519767</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>376258; 540180</t>
+          <t>503648; 599034</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>368865; 439813</t>
+          <t>368079; 443924</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>507321; 592332</t>
+          <t>512065; 603803</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>333507; 410704</t>
+          <t>337268; 413031</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>305337; 415367</t>
+          <t>388067; 448988</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>838333; 946159</t>
+          <t>838459; 950149</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1204086; 1338789</t>
+          <t>1206019; 1337771</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>796671; 906223</t>
+          <t>790208; 899820</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>757706; 944760</t>
+          <t>916155; 1027041</t>
         </is>
       </c>
     </row>
